--- a/product_upload/packages/22/file.xlsx
+++ b/product_upload/packages/22/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -846,6 +851,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>FLUTAB TABLET</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-19A72BDC9745</t>
         </is>
       </c>
@@ -869,7 +879,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1040,6 +1050,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>FLUTAB Sinus TABLETS</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-49C13DFC230B</t>
         </is>
       </c>
@@ -1063,7 +1078,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1230,6 +1245,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>DIVIDO 75MG DUAL RELEASE CAP</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-11D96D0A4CDF</t>
         </is>
       </c>
@@ -1253,7 +1273,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1424,6 +1444,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>DIUSEMIDE 40 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-A8B47C8D8D2D</t>
         </is>
       </c>
@@ -1447,7 +1472,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1622,6 +1647,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>DISPRIN</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-278287EAE15D</t>
         </is>
       </c>
@@ -1645,7 +1675,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1812,6 +1842,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>DISPERCAM GEL 0.5%</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-2A880EAE6E05</t>
         </is>
       </c>
@@ -1835,7 +1870,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2002,6 +2037,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>DOGMATIL CAPS 50MG</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-1F506661DE5A</t>
         </is>
       </c>
@@ -2025,7 +2065,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2184,6 +2224,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>DONECEPT 5MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-3F176A0A7356</t>
         </is>
       </c>
@@ -2207,7 +2252,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2378,6 +2423,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>DOMPY 10MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-1263EF930606</t>
         </is>
       </c>
@@ -2401,7 +2451,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2564,6 +2614,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>DOMPY 0.1% ORAL SUSPENTION</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-BD0F8A805F76</t>
         </is>
       </c>
@@ -2587,7 +2642,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2750,6 +2805,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>DOLVIC- K 50 MG F- C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-6EDBF080DA58</t>
         </is>
       </c>
@@ -2773,7 +2833,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2944,6 +3004,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>DOLGIT CREAM 50MG-G</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-4537358D9C3C</t>
         </is>
       </c>
@@ -2967,7 +3032,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3136,6 +3201,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>DOGMATIL FORT TAB 200MG</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-01C10F59F088</t>
         </is>
       </c>
@@ -3159,7 +3229,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3334,6 +3404,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>DIFFERIN 0.1% GEL</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-818075E55BCE</t>
         </is>
       </c>
@@ -3357,7 +3432,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3528,6 +3603,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>DIFFERIN 0.1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-886AE5CA397A</t>
         </is>
       </c>
@@ -3551,7 +3631,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3726,6 +3806,11 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>DICYNONE 500 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-D30251A4B5F9</t>
         </is>
       </c>
@@ -3749,7 +3834,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3912,6 +3997,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>DICLON 1% EMULGEL</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-743DA5098A81</t>
         </is>
       </c>
@@ -3935,7 +4025,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4102,6 +4192,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>DICLOMAX 50 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-104AD6EFBCA0</t>
         </is>
       </c>
@@ -4125,7 +4220,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4280,6 +4375,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>DICLOMAX 25MG TAB</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-0D3FF7C3CABE</t>
         </is>
       </c>
@@ -4303,7 +4403,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4474,6 +4574,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>DICLOMAX 1% EMULGEL</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-1EBAB8C94713</t>
         </is>
       </c>
@@ -4497,7 +4602,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4664,6 +4769,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>DICLOGESIC 50MG SUPPOSITORY</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-23A940A3DDE5</t>
         </is>
       </c>
@@ -4687,7 +4797,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4858,6 +4968,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>DICLOGESIC</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-6BC8CFD0F3A8</t>
         </is>
       </c>
@@ -4881,7 +4996,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5052,6 +5167,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>DILANYL SYRUP</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-35DC0EB37797</t>
         </is>
       </c>
@@ -5075,7 +5195,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5242,6 +5362,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>DIOVAN 80MG TAB</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-D3AB71E4601B</t>
         </is>
       </c>
@@ -5265,7 +5390,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5428,6 +5553,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>DIOVAN 40MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-FFF6D04CEE7E</t>
         </is>
       </c>
@@ -5451,7 +5581,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5622,6 +5752,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>DIOVAN 160MGTAB</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-039DEA05E0A5</t>
         </is>
       </c>
@@ -5645,7 +5780,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5804,6 +5939,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>DINTOINA TAB 100MG</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-293E0AE04275</t>
         </is>
       </c>
@@ -5827,7 +5967,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5998,6 +6138,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>DILZEM RETARD</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-2A5CF35C843F</t>
         </is>
       </c>
@@ -6021,7 +6166,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6192,6 +6337,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>DIOVAN 320MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-B3B117D8F550</t>
         </is>
       </c>
@@ -6215,7 +6365,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6386,6 +6536,11 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>DICLOGESIC</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-ADD0B2D1ACDD</t>
         </is>
       </c>
@@ -6409,7 +6564,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6576,6 +6731,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>EARCALM</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-AADE0A11E985</t>
         </is>
       </c>
@@ -6599,7 +6759,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6764,6 +6924,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>DUSPATALIN 200MG PROLONGED RELEASE CAPS</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-DC41C4BC4EA4</t>
         </is>
       </c>
@@ -6787,7 +6952,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6954,6 +7119,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>DUSPAMEN 135MG TAB</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-20DF0647218F</t>
         </is>
       </c>
@@ -6977,7 +7147,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7148,6 +7318,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>DUROGESIC TTS 75 Ug-HOUR</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-D079745196CD</t>
         </is>
       </c>
@@ -7171,7 +7346,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7330,6 +7505,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>DUROGESIC TTS 50 Ug-HOUR</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-8DA8D17565E1</t>
         </is>
       </c>
@@ -7353,7 +7533,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7516,6 +7696,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>DUROGESIC TTS 25 Ug-HOUR</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-E9A4BD96C636</t>
         </is>
       </c>
@@ -7539,7 +7724,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7698,6 +7883,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>DUROGESIC TTS 100 Ug-HOUR</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-F930CD91D334</t>
         </is>
       </c>
@@ -7721,7 +7911,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7880,6 +8070,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>DUROGESIC 12MCG-H TRASDERMAL PATCHES</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-CB3E81804769</t>
         </is>
       </c>
@@ -7903,7 +8098,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8070,6 +8265,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>DURATEARS OCULAR OINT.</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-649998965218</t>
         </is>
       </c>
@@ -8093,7 +8293,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8264,6 +8464,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>DURACAN 150MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-5642580F31F4</t>
         </is>
       </c>
@@ -8287,7 +8492,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8450,6 +8655,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>ELDOQUIN CREAM 2%</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-C66B8C9DA311</t>
         </is>
       </c>
@@ -8473,7 +8683,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8644,6 +8854,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>DUPHALAC ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-29D6D2A19E38</t>
         </is>
       </c>
@@ -8667,7 +8882,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8840,6 +9055,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>EFEXOR XR 150 MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-4ADB1335459E</t>
         </is>
       </c>
@@ -8863,7 +9083,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -9026,6 +9246,11 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>ECZADERM 0.1% W-W OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-13AA61E013A0</t>
         </is>
       </c>
@@ -9049,7 +9274,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9220,6 +9445,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>ECZADERM 0.1% W-W CREAM</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-F01EB46879AD</t>
         </is>
       </c>
@@ -9243,7 +9473,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9402,6 +9632,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>EBIXA 20MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-580BBF2EC9E4</t>
         </is>
       </c>
@@ -9425,7 +9660,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9588,6 +9823,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>EBIXA 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-2C5B44534A94</t>
         </is>
       </c>
@@ -9611,7 +9851,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9784,6 +10024,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>EFEXOR XR 75 MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-ABF8A5CC9EE3</t>
         </is>
       </c>
@@ -9807,7 +10052,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9974,6 +10219,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>DOXIVENIL</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-605B39D14F32</t>
         </is>
       </c>
@@ -9997,7 +10247,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10172,6 +10422,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>DOSTINEX 0.5MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-26410B1F2537</t>
         </is>
       </c>
@@ -10195,7 +10450,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10370,6 +10625,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>DOSTINEX 0.5MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-F048CE3C1DC6</t>
         </is>
       </c>
@@ -10393,7 +10653,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10568,6 +10828,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>DOROFEN 500-50 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-7774CBE0D047</t>
         </is>
       </c>
@@ -10591,7 +10856,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10750,6 +11015,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>DOXYCIN</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-EC827568AA44</t>
         </is>
       </c>
@@ -10773,7 +11043,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10944,6 +11214,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>DRAMYLIN PEDIATRIC SYRUP</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-AC6A559C9691</t>
         </is>
       </c>
@@ -10967,7 +11242,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11138,6 +11413,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>DRAMYLIN SYRUP</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-605E5D41E278</t>
         </is>
       </c>
@@ -11161,7 +11441,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11336,6 +11616,11 @@
       </c>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>DUODART Capsule</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-CC9858A071FA</t>
         </is>
       </c>
@@ -11359,7 +11644,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11512,6 +11797,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>DUBAM SPRAY</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-0E4EF2AD7BA8</t>
         </is>
       </c>
@@ -11535,7 +11825,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11698,6 +11988,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>DROLATE 70 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-F61C48941B50</t>
         </is>
       </c>
@@ -11721,7 +12016,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11884,6 +12179,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>DROF 2% SHAMPOO</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-DF6E6DC10E10</t>
         </is>
       </c>
@@ -11907,7 +12207,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12070,6 +12370,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>DICLOGESIC</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-5866A22CCBA7</t>
         </is>
       </c>
@@ -12093,7 +12398,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12264,6 +12569,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>DICLAC 75MG ID TABLETS</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-1D97FA0C89A4</t>
         </is>
       </c>
@@ -12287,7 +12597,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12460,6 +12770,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>DIAMICRON MR TABLET</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-591F8B3B9BE5</t>
         </is>
       </c>
@@ -12483,7 +12798,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12660,6 +12975,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>DIAMICRON 60MG MR TABLET</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-7C193E5F24B2</t>
         </is>
       </c>
@@ -12683,7 +13003,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12846,6 +13166,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>DEXTROSE,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-7C399056F027</t>
         </is>
       </c>
@@ -12869,7 +13194,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -13036,6 +13361,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>0.18% W/V SODIUM CHLORIDE and 5% W/V DEXTROSE intravenous infusion</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-DD7041BFED3C</t>
         </is>
       </c>
@@ -13059,7 +13389,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13222,6 +13552,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>0.18% W/V SODIUM CHLORIDE and 5% W/V DEXTROSE intravenous infusion</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-3F103716C98A</t>
         </is>
       </c>
@@ -13245,7 +13580,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13412,6 +13747,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>0.18% W/V SODIUM CHLORIDE and 5% W/V DEXTROSE intravenous infusion</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-74E257D95425</t>
         </is>
       </c>
@@ -13435,7 +13775,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13598,6 +13938,11 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>DEXTROSE 50%</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-A2C6CF25C0BE</t>
         </is>
       </c>
@@ -13621,7 +13966,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13780,6 +14125,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>DEXTROSE 50%</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-7745C883D96D</t>
         </is>
       </c>
@@ -13803,7 +14153,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13962,6 +14312,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>DEXTROSE 50%</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-00AC56A90FAF</t>
         </is>
       </c>
@@ -13985,7 +14340,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14152,6 +14507,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>50% w/v DEXTROSE intravenous infusion</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-C8ECC8EAD670</t>
         </is>
       </c>
@@ -14175,7 +14535,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14338,6 +14698,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>DEXTROSE 50%</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-EC569E1E105C</t>
         </is>
       </c>
@@ -14361,7 +14726,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14524,6 +14889,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>DEXTROSE 50%</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-4572DB3A70B4</t>
         </is>
       </c>
@@ -14547,7 +14917,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14706,6 +15076,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>DEXTROSE 50%</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-948957AAEE5F</t>
         </is>
       </c>
@@ -14729,7 +15104,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14892,6 +15267,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>DEXTROSE 50%</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-8C4E17FFB4F3</t>
         </is>
       </c>
@@ -14915,7 +15295,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15078,6 +15458,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>50%W/V DESTROSE intravenous infusion</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-0CB620ECC369</t>
         </is>
       </c>
@@ -15101,7 +15486,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15260,6 +15645,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%+SOD.CHLORIDE 0.20% INJ</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-396CC3071B86</t>
         </is>
       </c>
@@ -15283,7 +15673,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15450,6 +15840,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%+SOD.CHLORIDE 0.20% INJ</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-65BE88E4495D</t>
         </is>
       </c>
@@ -15473,7 +15868,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15640,6 +16035,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>0.18% W/V SODIUM CHLORIDE and 5% W/V DEXTROSE intravenous infusion</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-222B8FF389C0</t>
         </is>
       </c>
@@ -15663,7 +16063,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15838,6 +16238,11 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>DEXTROSE,N.SALINE</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-559E1F917618</t>
         </is>
       </c>
@@ -15861,7 +16266,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16024,6 +16429,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>DEXTROSE,N.SALINE</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-D02BB252F798</t>
         </is>
       </c>
@@ -16047,7 +16457,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16210,6 +16620,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>DEXTROSE,N.SALINE</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-52DBFD5BD348</t>
         </is>
       </c>
@@ -16233,7 +16648,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16396,6 +16811,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>DEXTROSE,N.SALINE</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-942F4707372C</t>
         </is>
       </c>
@@ -16419,7 +16839,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16582,6 +17002,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>DEXTROSE, SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-9CF9D58BC8A1</t>
         </is>
       </c>
@@ -16605,7 +17030,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16768,6 +17193,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>DEXTROSE, SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-0B0E4FA1B107</t>
         </is>
       </c>
@@ -16791,7 +17221,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16958,6 +17388,11 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>0.18% W/V SODIUM CHLORIDE and 5% W/V DEXTROSE intravenous infusion</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-040D0CB77B2B</t>
         </is>
       </c>
@@ -16981,7 +17416,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17148,6 +17583,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>DEXTROSE, SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-1C5C7BC4E892</t>
         </is>
       </c>
@@ -17171,7 +17611,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17330,6 +17770,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t xml:space="preserve">DEXTROSE 70% SOLUTION  </t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-79AEC3FEE6FA</t>
         </is>
       </c>
@@ -17353,7 +17798,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17516,6 +17961,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>DEXTROSE SOLUTION 70%</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-7BBBA3055DE9</t>
         </is>
       </c>
@@ -17539,7 +17989,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17698,6 +18148,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>DEXTROSE, HARTMANNS</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-F9A1455C3030</t>
         </is>
       </c>
@@ -17721,7 +18176,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17890,6 +18345,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>DICETEL TAB 50MG</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-8D53104CE32C</t>
         </is>
       </c>
@@ -17913,7 +18373,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18080,6 +18540,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>ELDOQUIN CREAM 2%</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-A8CD3E346781</t>
         </is>
       </c>
@@ -18103,7 +18568,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18266,6 +18731,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>CO-VALISTA</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-A3516DBB60C5</t>
         </is>
       </c>
@@ -18289,7 +18759,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18452,6 +18922,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>ELDOQUIN FORT 4% CREAM</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-769661CADF77</t>
         </is>
       </c>
@@ -18475,7 +18950,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18646,6 +19121,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>ELICA 0.1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-12F208257120</t>
         </is>
       </c>
@@ -18669,7 +19149,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18828,6 +19308,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>FEVADOL FAST 500MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-BCF73028BC31</t>
         </is>
       </c>
@@ -18851,7 +19336,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19022,6 +19507,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>FEVADOL EXTRA TAB.</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-64C9DE2049CA</t>
         </is>
       </c>
@@ -19045,7 +19535,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19204,6 +19694,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>FEVADOL COLD &amp; FLU TABLETS</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-5C912A710EBD</t>
         </is>
       </c>
@@ -19227,7 +19722,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19390,6 +19885,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>FEVADOL 500MG TAB</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-9B6F39B1D01D</t>
         </is>
       </c>
@@ -19413,7 +19913,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19575,6 +20075,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>FEVADOL 350MG SUPPOSITORY</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-443E5111F9D1</t>
         </is>
@@ -19591,7 +20096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19637,100 +20142,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19762,7 +20272,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19777,92 +20287,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-91220</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>70.41</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>142</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19894,7 +20409,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19909,92 +20424,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-22554</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>119.12</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>143</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20026,7 +20546,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20041,92 +20561,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-45380</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>460.78</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>144</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20158,7 +20683,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20173,92 +20698,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-72194</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>342.2</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>145</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20290,7 +20820,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20305,92 +20835,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-29825</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>382.54</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>146</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20422,7 +20957,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20437,92 +20972,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-22482</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>383.07</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>147</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20554,7 +21094,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20569,92 +21109,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-55197</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>61.36</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>148</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20686,7 +21231,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20701,92 +21246,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-53490</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>321.71</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>149</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20818,7 +21368,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20833,92 +21383,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-86082</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>463.59</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>150</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20950,7 +21505,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20965,92 +21520,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-15875</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>456.37</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>151</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21082,7 +21642,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21097,92 +21657,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-87560</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>309.62</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>152</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21199,7 +21764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21305,6 +21870,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21340,7 +21915,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21405,6 +21980,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-7E161AEA5A50</t>
         </is>
@@ -21441,7 +22026,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21506,6 +22091,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-541E4AFA7334</t>
         </is>
@@ -21542,7 +22137,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21607,6 +22202,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-0B785D15CBF6</t>
         </is>
@@ -21643,7 +22248,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21708,6 +22313,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-D7CBD1D112DA</t>
         </is>
@@ -21744,7 +22359,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21809,6 +22424,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-2F8E80E0A213</t>
         </is>
@@ -21845,7 +22470,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21910,6 +22535,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-972C5C4A41BE</t>
         </is>
@@ -21946,7 +22581,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22011,6 +22646,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-0CBF1106ECF9</t>
         </is>
@@ -22047,7 +22692,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22112,6 +22757,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-390C02C9E9DE</t>
         </is>
@@ -22148,7 +22803,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22213,6 +22868,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-6D9A7AB49C06</t>
         </is>
@@ -22249,7 +22914,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22314,6 +22979,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-684978E5DA10</t>
         </is>
@@ -22350,7 +23025,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22415,6 +23090,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-3EE94797CEBE</t>
         </is>
@@ -22451,7 +23136,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22516,6 +23201,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-D7F32BB0348A</t>
         </is>
@@ -22552,7 +23247,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22617,6 +23312,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-444154FE4072</t>
         </is>
@@ -22653,7 +23358,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22718,6 +23423,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-73FEFAAC9871</t>
         </is>
@@ -22754,7 +23469,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22819,6 +23534,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-26DB4D2AA21D</t>
         </is>
@@ -22855,7 +23580,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22920,6 +23645,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-510902108F94</t>
         </is>
@@ -22956,7 +23691,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23021,6 +23756,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-56DC2010F867</t>
         </is>
@@ -23057,7 +23802,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23122,6 +23867,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-ABCFE152196A</t>
         </is>
@@ -23158,7 +23913,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23223,6 +23978,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-793773816010</t>
         </is>
@@ -23259,7 +24024,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23324,6 +24089,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-45DAEC464A4D</t>
         </is>

--- a/product_upload/packages/22/file.xlsx
+++ b/product_upload/packages/22/file.xlsx
@@ -1683,8 +1683,16 @@
           <t>9440121815-611-751118797466</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DISPERCAM GEL 0.5%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>DISPERCAM GEL 0.5% detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -2073,8 +2081,16 @@
           <t>8762263199-175-403096947047</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DONECEPT 5MG TABLET</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>DONECEPT 5MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2650,8 +2666,16 @@
           <t>8030216647-106-882840546903</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DOLVIC- K 50 MG F- C TABLETS</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>DOLVIC- K 50 MG F- C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -3842,8 +3866,16 @@
           <t>6141917416-610-872678315147</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DICLON 1% EMULGEL</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>DICLON 1% EMULGEL detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -4228,8 +4260,16 @@
           <t>2541216607-196-019729568316</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DICLOMAX 25MG TAB</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>DICLOMAX 25MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -5788,8 +5828,16 @@
           <t>4469614032-871-220953965401</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DINTOINA TAB 100MG</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>DINTOINA TAB 100MG detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -7354,8 +7402,16 @@
           <t>5748088753-986-878027462373</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DUROGESIC TTS 50 Ug-HOUR</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>DUROGESIC TTS 50 Ug-HOUR detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7732,8 +7788,16 @@
           <t>0692609537-074-740205497076</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DUROGESIC TTS 100 Ug-HOUR</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>DUROGESIC TTS 100 Ug-HOUR detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7919,8 +7983,16 @@
           <t>3083573544-760-530458925852</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DUROGESIC 12MCG-H TRASDERMAL PATCHES</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>DUROGESIC 12MCG-H TRASDERMAL PATCHES detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -8500,8 +8572,16 @@
           <t>7551467048-832-508052393910</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ELDOQUIN CREAM 2%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ELDOQUIN CREAM 2% detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -9091,8 +9171,16 @@
           <t>5625663975-557-602003043542</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ECZADERM 0.1% W-W OINTMENT</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ECZADERM 0.1% W-W OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9481,8 +9569,16 @@
           <t>5449211482-764-806861940489</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EBIXA 20MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>EBIXA 20MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -10864,8 +10960,16 @@
           <t>9076153106-404-387911292636</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DOXYCIN</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>DOXYCIN detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -11652,8 +11756,16 @@
           <t>3655389909-304-716564640845</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DUBAM SPRAY</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>DUBAM SPRAY detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11833,8 +11945,16 @@
           <t>6020661700-687-340163925190</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DROLATE 70 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>DROLATE 70 MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -12024,8 +12144,16 @@
           <t>9957467320-035-111828768740</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DROF 2% SHAMPOO</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>DROF 2% SHAMPOO detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12215,8 +12343,16 @@
           <t>8286416802-924-536601079835</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DICLOGESIC</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>DICLOGESIC detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -13011,8 +13147,16 @@
           <t>9924040041-914-975288987419</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE,SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>DEXTROSE,SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13202,8 +13346,16 @@
           <t>7582792322-777-290767522245</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 0.18% W/V SODIUM CHLORIDE and 5% W/V DEXTROSE intravenous infusion</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>0.18% W/V SODIUM CHLORIDE and 5% W/V DEXTROSE intravenous infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13397,8 +13549,16 @@
           <t>2860994087-842-809759080639</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 0.18% W/V SODIUM CHLORIDE and 5% W/V DEXTROSE intravenous infusion</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>0.18% W/V SODIUM CHLORIDE and 5% W/V DEXTROSE intravenous infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13588,8 +13748,16 @@
           <t>0986317566-601-266582201432</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 0.18% W/V SODIUM CHLORIDE and 5% W/V DEXTROSE intravenous infusion</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>0.18% W/V SODIUM CHLORIDE and 5% W/V DEXTROSE intravenous infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13783,8 +13951,16 @@
           <t>2990611191-033-397960008763</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 50%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>DEXTROSE 50% detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13974,8 +14150,16 @@
           <t>0978899532-748-365924060095</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 50%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>DEXTROSE 50% detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14161,8 +14345,16 @@
           <t>4850506416-225-395706389624</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 50%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>DEXTROSE 50% detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -14543,8 +14735,16 @@
           <t>7636601952-781-713264604590</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 50%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>DEXTROSE 50% detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14734,8 +14934,16 @@
           <t>6686415587-493-307609694049</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 50%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>DEXTROSE 50% detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14925,8 +15133,16 @@
           <t>0996920289-234-356180839775</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 50%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>DEXTROSE 50% detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -15112,8 +15328,16 @@
           <t>6389723985-568-060413551762</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 50%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>DEXTROSE 50% detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -15303,8 +15527,16 @@
           <t>5700073115-052-550421750951</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 50%W/V DESTROSE intravenous infusion</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>50%W/V DESTROSE intravenous infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15494,8 +15726,16 @@
           <t>1912730123-816-634677497841</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%+SOD.CHLORIDE 0.20% INJ</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5%+SOD.CHLORIDE 0.20% INJ detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15681,8 +15921,16 @@
           <t>6850381139-937-756632273140</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%+SOD.CHLORIDE 0.20% INJ</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5%+SOD.CHLORIDE 0.20% INJ detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15876,8 +16124,16 @@
           <t>4603215401-342-572900451337</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 0.18% W/V SODIUM CHLORIDE and 5% W/V DEXTROSE intravenous infusion</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0.18% W/V SODIUM CHLORIDE and 5% W/V DEXTROSE intravenous infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -16274,8 +16530,16 @@
           <t>9050492223-693-019136687649</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE,N.SALINE</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>DEXTROSE,N.SALINE detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16465,8 +16729,16 @@
           <t>5645875991-656-731780011349</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE,N.SALINE</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>DEXTROSE,N.SALINE detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16656,8 +16928,16 @@
           <t>6580772865-515-364309871745</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE,N.SALINE</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>DEXTROSE,N.SALINE detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16847,8 +17127,16 @@
           <t>5078607741-156-646512507972</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE, SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>DEXTROSE, SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -17038,8 +17326,16 @@
           <t>4664079558-211-882210542706</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE, SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>DEXTROSE, SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -17229,8 +17525,16 @@
           <t>9425007142-421-548037412048</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 0.18% W/V SODIUM CHLORIDE and 5% W/V DEXTROSE intravenous infusion</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0.18% W/V SODIUM CHLORIDE and 5% W/V DEXTROSE intravenous infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17424,8 +17728,16 @@
           <t>9450320916-572-165091485395</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE, SOD.CHLORIDE</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>DEXTROSE, SOD.CHLORIDE detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17619,8 +17931,16 @@
           <t>4049498963-485-727823104403</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 70% SOLUTION</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>DEXTROSE 70% SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17806,8 +18126,16 @@
           <t>0129767476-415-683507874219</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE SOLUTION 70%</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>DEXTROSE SOLUTION 70% detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17997,8 +18325,16 @@
           <t>5762601055-834-285798391060</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE, HARTMANNS</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>DEXTROSE, HARTMANNS detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18381,8 +18717,16 @@
           <t>1020942982-065-638279493461</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ELDOQUIN CREAM 2%</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ELDOQUIN CREAM 2% detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18576,8 +18920,16 @@
           <t>8615722628-856-845649030847</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-VALISTA</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>CO-VALISTA detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18767,8 +19119,16 @@
           <t>8653671540-852-578773271048</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ELDOQUIN FORT 4% CREAM</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ELDOQUIN FORT 4% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -19157,8 +19517,16 @@
           <t>1200525324-675-081767242615</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FEVADOL FAST 500MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>FEVADOL FAST 500MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -19543,8 +19911,16 @@
           <t>4800755123-443-708967529205</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FEVADOL COLD &amp; FLU TABLETS</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>FEVADOL COLD &amp; FLU TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -19730,8 +20106,16 @@
           <t>2112544019-661-273836808581</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FEVADOL 500MG TAB</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>FEVADOL 500MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19921,8 +20305,16 @@
           <t>0937506532-249-249055269460</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FEVADOL 350MG SUPPOSITORY</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>FEVADOL 350MG SUPPOSITORY detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/22/file.xlsx
+++ b/product_upload/packages/22/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20534,7 +20534,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22237,40 +22237,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22350,38 +22355,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>93.40000000000001</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-7E161AEA5A50</t>
         </is>
@@ -22461,38 +22471,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>151.93</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-541E4AFA7334</t>
         </is>
@@ -22572,38 +22587,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>39.56</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-0B785D15CBF6</t>
         </is>
@@ -22683,38 +22703,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>468.35</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-D7CBD1D112DA</t>
         </is>
@@ -22794,38 +22819,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>230.5</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-2F8E80E0A213</t>
         </is>
@@ -22905,38 +22935,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>262.7</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-972C5C4A41BE</t>
         </is>
@@ -23016,38 +23051,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>260.24</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-0CBF1106ECF9</t>
         </is>
@@ -23127,38 +23167,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>287.95</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-390C02C9E9DE</t>
         </is>
@@ -23238,38 +23283,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>140.58</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-6D9A7AB49C06</t>
         </is>
@@ -23349,38 +23399,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>202.54</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-684978E5DA10</t>
         </is>
@@ -23460,38 +23515,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>42.38</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-3EE94797CEBE</t>
         </is>
@@ -23571,38 +23631,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>162.99</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-D7F32BB0348A</t>
         </is>
@@ -23682,38 +23747,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>463.96</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-444154FE4072</t>
         </is>
@@ -23793,38 +23863,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>416.72</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-73FEFAAC9871</t>
         </is>
@@ -23904,38 +23979,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>92.23</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-26DB4D2AA21D</t>
         </is>
@@ -24015,38 +24095,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>69.81999999999999</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-510902108F94</t>
         </is>
@@ -24126,38 +24211,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>309.42</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-56DC2010F867</t>
         </is>
@@ -24237,38 +24327,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>449.43</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-ABCFE152196A</t>
         </is>
@@ -24348,38 +24443,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>314.32</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-793773816010</t>
         </is>
@@ -24459,38 +24559,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>258.22</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-45DAEC464A4D</t>
         </is>
